--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address|Address}
+    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address}
 </t>
   </si>
   <si>
@@ -1190,7 +1190,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.85546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="341">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -801,6 +801,191 @@
     <t>./Qualifications.Value</t>
   </si>
   <si>
+    <t>Practitioner.qualification.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>Practitioner.qualification.period</t>
   </si>
   <si>
@@ -861,6 +1046,39 @@
   </si>
   <si>
     <t>./Languages.LanguageSpokenCode</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.id</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding.system</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding.version</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding.code</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding.display</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.text</t>
   </si>
 </sst>
 </file>
@@ -1177,11 +1395,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.8984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.8984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.9375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.9375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1208,14 +1426,14 @@
     <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.65625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="47.515625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -3857,7 +4075,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>241</v>
       </c>
@@ -3876,7 +4094,7 @@
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
@@ -3997,18 +4215,16 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4056,7 +4272,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4068,16 +4284,16 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4085,21 +4301,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4111,15 +4327,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>257</v>
+        <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4156,37 +4374,37 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4195,12 +4413,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4214,28 +4432,28 @@
         <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4260,13 +4478,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4284,7 +4502,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4299,20 +4517,2536 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="O30" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN27">
+  <autoFilter ref="A1:AN49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4322,7 +7056,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI26">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="295">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -845,123 +845,6 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Practitioner.qualification.code.coding.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
     <t>Practitioner.qualification.code.text</t>
   </si>
   <si>
@@ -1055,27 +938,6 @@
   </si>
   <si>
     <t>Practitioner.communication.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.communication.coding.id</t>
-  </si>
-  <si>
-    <t>Practitioner.communication.coding.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.communication.coding.system</t>
-  </si>
-  <si>
-    <t>Practitioner.communication.coding.version</t>
-  </si>
-  <si>
-    <t>Practitioner.communication.coding.code</t>
-  </si>
-  <si>
-    <t>Practitioner.communication.coding.display</t>
-  </si>
-  <si>
-    <t>Practitioner.communication.coding.userSelected</t>
   </si>
   <si>
     <t>Practitioner.communication.text</t>
@@ -1395,11 +1257,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.9375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.9375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.8984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.8984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -4529,7 +4391,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>263</v>
       </c>
@@ -4548,25 +4410,29 @@
         <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>223</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>224</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4614,7 +4480,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4626,13 +4492,13 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4643,21 +4509,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4669,18 +4535,18 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -4716,40 +4582,40 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>227</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4757,10 +4623,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4780,23 +4646,19 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4844,7 +4706,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4859,10 +4721,10 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4871,12 +4733,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4887,30 +4749,32 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4934,13 +4798,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4958,13 +4822,13 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
@@ -4973,24 +4837,24 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5004,27 +4868,25 @@
         <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>223</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>281</v>
+        <v>224</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>282</v>
+        <v>225</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5072,7 +4934,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5084,13 +4946,13 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5101,21 +4963,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5124,21 +4986,21 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>223</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5174,51 +5036,51 @@
         <v>77</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
-      <c r="A34" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5229,10 +5091,10 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
@@ -5241,19 +5103,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>257</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5302,13 +5164,13 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -5317,10 +5179,10 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5329,12 +5191,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5348,7 +5210,7 @@
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
@@ -5360,16 +5222,16 @@
         <v>223</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>265</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>305</v>
+        <v>266</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5418,7 +5280,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5433,10 +5295,10 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>308</v>
+        <v>269</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5445,1608 +5307,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
-      <c r="A36" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="P36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="P38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" hidden="true">
-      <c r="A40" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN49">
+  <autoFilter ref="A1:AN35">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7056,7 +5318,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI34">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
